--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260729.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>32,782</t>
+          <t>32,396</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.62%</t>
+          <t>10.27%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>79,241</t>
+          <t>78,307</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>9.98%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>91,403</t>
+          <t>90,325</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>7.09%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,979</t>
+          <t>35,555</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.25%</t>
+          <t>7.03%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>197,483</t>
+          <t>195,156</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.70%</t>
+          <t>6.08%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>105,029</t>
+          <t>103,791</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>113,909</t>
+          <t>112,566</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
@@ -765,78 +765,78 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,610</t>
+          <t>19,379</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>49,580</t>
+          <t>117,083</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>59,662</t>
+          <t>48,995</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>118,479</t>
+          <t>58,959</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>54,874</t>
+          <t>54,227</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>137,926</t>
+          <t>136,301</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -897,56 +897,56 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,800</t>
+          <t>22,531</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,593</t>
+          <t>62,303</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>63,046</t>
+          <t>24,304</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>37,218</t>
+          <t>36,780</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>51,820</t>
+          <t>51,210</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1007,95 +1007,95 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>50,330</t>
+          <t>49,736</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,472</t>
+          <t>77,001</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>77,920</t>
+          <t>50,060</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>50,657</t>
+          <t>32,510</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>32,898</t>
+          <t>47,027</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,132 +1107,132 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>22,524</t>
+          <t>30,445</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>30,808</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>47,588</t>
+          <t>95,063</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,898</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>20,956</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>96,197</t>
+          <t>20,709</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1249,122 +1249,122 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>75,970</t>
+          <t>75,074</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>4,980</t>
+          <t>145,945</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,112</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>30,676</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>147,686</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>13,410</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>31,057</t>
+          <t>30,691</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1425,56 +1425,56 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10,773</t>
+          <t>10,646</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>26,089</t>
+          <t>43,483</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>44,002</t>
+          <t>25,781</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,584</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1513,29 +1513,29 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,320</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,909</t>
+          <t>94,502</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,22 +1547,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>95,629</t>
+          <t>6,827</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,695</t>
+          <t>3,651</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,948</t>
+          <t>5,878</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>23,519</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,44 +1635,44 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,873</t>
+          <t>8,021</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,117</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,673</t>
+          <t>18,453</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>38,717</t>
+          <t>38,261</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>103,135,552</t>
+          <t>114,139,833</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
